--- a/newShipmentTemplate.xlsx
+++ b/newShipmentTemplate.xlsx
@@ -1005,121 +1005,121 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" s="21">
-      <c r="A2" s="25" t="inlineStr"/>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
-        <is>
-          <t>Warehouse CA-2</t>
-        </is>
-      </c>
-      <c r="D2" s="25" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="E2" s="25" t="inlineStr">
-        <is>
-          <t>5678 Kingsway</t>
-        </is>
-      </c>
-      <c r="F2" s="25" t="inlineStr">
-        <is>
-          <t>V5H 2A9</t>
-        </is>
-      </c>
-      <c r="G2" s="25" t="inlineStr">
-        <is>
-          <t>Burnaby</t>
-        </is>
-      </c>
-      <c r="H2" s="25" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="I2" s="25" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J2" s="25" t="inlineStr">
-        <is>
-          <t>shipper2Karl@gmail.com</t>
-        </is>
-      </c>
-      <c r="K2" s="25" t="inlineStr">
-        <is>
-          <t>Maria Aldovino</t>
-        </is>
-      </c>
-      <c r="L2" s="25" t="inlineStr">
-        <is>
-          <t>13438000120</t>
-        </is>
-      </c>
-      <c r="M2" s="25" t="inlineStr">
-        <is>
-          <t>1034 Valour Rd</t>
-        </is>
-      </c>
-      <c r="N2" s="25" t="inlineStr"/>
-      <c r="O2" s="25" t="inlineStr">
-        <is>
-          <t>R3G 3B7</t>
-        </is>
-      </c>
-      <c r="P2" s="25" t="inlineStr">
-        <is>
-          <t>WINNIPEG</t>
-        </is>
-      </c>
-      <c r="Q2" s="25" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="R2" s="25" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Warehouse CA-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>416-555-0101</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1234 Finch Ave W</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>M3J 2X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="S2" s="25" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>shipper1Jay@gmail.com</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mina benahmed</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>18257980329</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>57 Rue Guilbault</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>H7N 4N2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LAVAL</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>PQ</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U2" s="25" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V2" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="W2" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="X2" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" s="25" t="inlineStr">
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>YOUR_PACKAGING</t>
         </is>
       </c>
-      <c r="Z2" s="25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="AA2" s="25" t="inlineStr">
-        <is>
-          <t>MVB × 1, RB1 × 1</t>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>RB1 × 1</t>
         </is>
       </c>
     </row>
@@ -1132,73 +1132,73 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warehouse CA-1</t>
+          <t>Warehouse CA-3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>514-555-0222</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1234 Finch Ave W</t>
+          <t>910 Rue Sainte-Catherine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M3J 2X2</t>
+          <t>H3B 1E2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>PQ</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>shipper1Jay@gmail.com</t>
+          <t>shipper3Bob@gmail.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ping Shi</t>
+          <t>Liliana Iantorno-Jasmin</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12048175863</t>
+          <t>12262405236</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>312-10405 Saskatchewan Dr NW</t>
+          <t>211-277 Preston St, 211</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>T6E 4R9</t>
+          <t>P4N 3N9</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>EDMONTON</t>
+          <t>TIMMINS</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1210,21 +1210,21 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>G300 × 1</t>
+          <t>RB1 × 1</t>
         </is>
       </c>
     </row>
@@ -1251,73 +1251,73 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warehouse CA-1</t>
+          <t>Warehouse CA-3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>514-555-0222</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1234 Finch Ave W</t>
+          <t>910 Rue Sainte-Catherine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M3J 2X2</t>
+          <t>H3B 1E2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>PQ</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>shipper1Jay@gmail.com</t>
+          <t>shipper3Bob@gmail.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sandra Huhtala</t>
+          <t>Cinu George</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18257980303</t>
+          <t>12362011721</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Box 159 Rorketon</t>
+          <t>11791 Seacliff Rd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R0L 1R0</t>
+          <t>V7A 3J6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RORKETON</t>
+          <t>RICHMOND</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1329,11 +1329,11 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>CTB × 1</t>
+          <t>SVB × 1</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>604-555-0188</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1410,28 +1410,28 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bev Simpson</t>
+          <t>Hua Tang</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12362011734</t>
+          <t>18257980317</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>75 Alford Cres, 53</t>
+          <t>28 Interchange Way, 1707</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M1B 4E5</t>
+          <t>L4K 0P8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SCARBOROUGH</t>
+          <t>CONCORD</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1448,18 +1448,18 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="X5" t="n">
         <v>5</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>LVB × 1</t>
+          <t>STB × 1</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>416-555-0101</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1529,33 +1529,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Balachandran Nedumaran</t>
+          <t>phieu -lu</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15873166142</t>
+          <t>18257976582</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1750 Hoxton St</t>
+          <t>12135 96 St NW</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>L1Y 1B3</t>
+          <t>T5G 1V9</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PICKERING</t>
+          <t>EDMONTON</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1567,21 +1567,21 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V6" t="n">
         <v>25</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>CTB × 1</t>
+          <t>DLTB × 1</t>
         </is>
       </c>
     </row>
@@ -1608,73 +1608,73 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warehouse CA-3</t>
+          <t>Warehouse CA-2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>604-555-0188</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>910 Rue Sainte-Catherine</t>
+          <t>5678 Kingsway</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>H3B 1E2</t>
+          <t>V5H 2A9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Burnaby</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PQ</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>shipper3Bob@gmail.com</t>
+          <t>shipper2Karl@gmail.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Margaret Hall</t>
+          <t>Donna Bourque</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18257980335</t>
+          <t>12362011717</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5 Hillhurst Pl</t>
+          <t>26 Knox Street Miramichi N.B.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>K2E 5R5</t>
+          <t>E1N 4K1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NEPEAN</t>
+          <t>MIRAMICHI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1686,21 +1686,21 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="W7" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>DLTB × 1</t>
+          <t>LVB × 1</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>604-555-0188</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1767,33 +1767,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dany Jobin</t>
+          <t>Sylvie Turgeon</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12362011732</t>
+          <t>12048173892</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1278 Boul Renaud, maison</t>
+          <t>302 Bergeron</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>G7H 3N8</t>
+          <t>P0L 1N0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CHICOUTIMI</t>
+          <t>HEARST</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PQ</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1805,21 +1805,21 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
         <v>20</v>
       </c>
-      <c r="W8" t="n">
-        <v>18</v>
-      </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1833,962 +1833,136 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>STB × 1</t>
+          <t>CTB × 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="21">
-      <c r="A9" s="25" t="inlineStr"/>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>OUTBOUND</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Warehouse CA-1</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>1234 Finch Ave W</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>M3J 2X2</t>
-        </is>
-      </c>
-      <c r="G9" s="25" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="I9" s="25" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="inlineStr">
-        <is>
-          <t>shipper1Jay@gmail.com</t>
-        </is>
-      </c>
-      <c r="K9" s="25" t="inlineStr">
-        <is>
-          <t>Lisa Clifton</t>
-        </is>
-      </c>
-      <c r="L9" s="25" t="inlineStr">
-        <is>
-          <t>18257978002</t>
-        </is>
-      </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t>5377 Fairhaven Pl</t>
-        </is>
-      </c>
-      <c r="N9" s="25" t="inlineStr"/>
-      <c r="O9" s="25" t="inlineStr">
-        <is>
-          <t>V9V 1R4</t>
-        </is>
-      </c>
-      <c r="P9" s="25" t="inlineStr">
-        <is>
-          <t>NANAIMO</t>
-        </is>
-      </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Warehouse CA-2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>604-555-0188</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5678 Kingsway</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>V5H 2A9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Burnaby</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="R9" s="25" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="S9" s="25" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shipper2Karl@gmail.com</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Romanovska Romanovska</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>18257980269</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>415-238 McIntyre Cres, 415</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>V2M 4P7</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PRINCE GEORGE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="25" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="25" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V9" s="25" t="n">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
         <v>35</v>
       </c>
-      <c r="W9" s="25" t="n">
+      <c r="W9" t="n">
         <v>7</v>
       </c>
-      <c r="X9" s="25" t="n">
+      <c r="X9" t="n">
         <v>7</v>
       </c>
-      <c r="Y9" s="25" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>YOUR_PACKAGING</t>
         </is>
       </c>
-      <c r="Z9" s="25" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="AA9" s="25" t="inlineStr">
-        <is>
-          <t>RB1 × 2</t>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>RB1 × 1</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" s="21">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Warehouse CA-2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>5678 Kingsway</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>V5H 2A9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Burnaby</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>shipper2Karl@gmail.com</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Nimia Fernandez</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>18257980282</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2203-15 Martha Eaton Way, apt 2203</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>M6M 5B5</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NORTH YORK</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>20</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>SVB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" s="21">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Warehouse CA-1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1234 Finch Ave W</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>M3J 2X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>shipper1Jay@gmail.com</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>joseph lawrence</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>18257980327</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>22 Blucher St</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>P6A 2V4</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>SAULT STE. MARIE</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>30</v>
-      </c>
-      <c r="W11" t="n">
-        <v>12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>MVB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" s="21">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Warehouse CA-3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>910 Rue Sainte-Catherine</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>H3B 1E2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Montreal</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PQ</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>shipper3Bob@gmail.com</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>karen lajeunesse</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>12262413442</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1770 Paris St, 601</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>P3E 3C3</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>SUDBURY</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>20</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>CTB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" s="21">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Warehouse CA-3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>910 Rue Sainte-Catherine</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>H3B 1E2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Montreal</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PQ</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>shipper3Bob@gmail.com</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Bunny Low low</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>12362011742</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>9055 Ashwell Rd, #7</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>V2P 7S6</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>CHILLIWACK</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>CTB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" s="21">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Warehouse CA-3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>910 Rue Sainte-Catherine</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>H3B 1E2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Montreal</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PQ</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>shipper3Bob@gmail.com</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Pauline Sisoula</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>18257980286</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>56 Chartwell Lane</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>B3M 4E1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>HALIFAX</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>20</v>
-      </c>
-      <c r="W14" t="n">
-        <v>18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>STB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="21">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Warehouse CA-2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>5678 Kingsway</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>V5H 2A9</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Burnaby</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>shipper2Karl@gmail.com</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Cecelia Chung</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>15873293565</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>7416 178 Ave NW</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>T5Z 0M6</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>EDMONTON</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>20</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>SVB × 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="21">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>OUTBOUND</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Warehouse CA-2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>5678 Kingsway</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>V5H 2A9</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Burnaby</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>shipper2Karl@gmail.com</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Tina Evans</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>12362011744</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>40 Parkridge View SE, 212    BUZZ IN CODE 4204</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>T2J 7G6</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>CALGARY</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>35</v>
-      </c>
-      <c r="W16" t="n">
-        <v>13</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>YOUR_PACKAGING</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>LVB × 1</t>
-        </is>
-      </c>
-    </row>
+    <row r="10" ht="24" customHeight="1" s="21"/>
+    <row r="11" ht="24" customHeight="1" s="21"/>
+    <row r="12" ht="24" customHeight="1" s="21"/>
+    <row r="13" ht="24" customHeight="1" s="21"/>
+    <row r="14" ht="24" customHeight="1" s="21"/>
+    <row r="15" ht="24" customHeight="1" s="21"/>
+    <row r="16" ht="24" customHeight="1" s="21"/>
     <row r="17" ht="24" customHeight="1" s="21"/>
     <row r="18" ht="24" customHeight="1" s="21"/>
     <row r="19" ht="24" customHeight="1" s="21"/>
